--- a/config/Coding/VF5NP_BCM_F108.xlsx
+++ b/config/Coding/VF5NP_BCM_F108.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\Coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D57E8E-C31A-4615-82F9-053D57591C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19A79F0-68B9-4894-9A2E-BF6AE6FC1760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E56B9D97-442E-44A8-BFBF-6A4857FA0292}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E56B9D97-442E-44A8-BFBF-6A4857FA0292}"/>
   </bookViews>
   <sheets>
     <sheet name="CDS Coding" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="\">#N/A</definedName>
@@ -748,7 +747,7 @@
     <definedName name="AA\\\\\">#REF!</definedName>
     <definedName name="AA\\\\\\">#REF!</definedName>
     <definedName name="AAA">#REF!</definedName>
-    <definedName name="aaaa">[2]Selections!$A$2:$A$103</definedName>
+    <definedName name="aaaa">[1]Selections!$A$2:$A$103</definedName>
     <definedName name="aaaaa" hidden="1">{"RES-2000",#N/A,FALSE,"BL2000";"A1-2000",#N/A,FALSE,"BL2000";"A2-2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaaa" hidden="1">{"RES-2002",#N/A,FALSE,"BL2000";"A1-2002",#N/A,FALSE,"BL2000";"A2-2002",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaaaa" hidden="1">{"B10-2000",#N/A,FALSE,"BL2000"}</definedName>
@@ -759,8 +758,8 @@
     <definedName name="AAAAAAAAAAAAAAAA">RunParT</definedName>
     <definedName name="aaaaaaaaaaaaaaaaa" hidden="1">{"AnaM1",#N/A,FALSE,"AnalisisM";"AnaM2",#N/A,FALSE,"AnalisisM";"AnaM3",#N/A,FALSE,"AnalisisM"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaaaaaaaaaa" hidden="1">{"COMJPN2000",#N/A,FALSE,"BL2000"}</definedName>
-    <definedName name="aaab">[2]Selections!$A$2:$A$103</definedName>
-    <definedName name="aac">[2]Selections!$A$2:$A$103</definedName>
+    <definedName name="aaab">[1]Selections!$A$2:$A$103</definedName>
+    <definedName name="aac">[1]Selections!$A$2:$A$103</definedName>
     <definedName name="ab" hidden="1">{"HS_USA",#N/A,FALSE,"Base"}</definedName>
     <definedName name="ABC" hidden="1">{"INCPRE2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="abcd" hidden="1">{"PT2000",#N/A,FALSE,"BL2000"}</definedName>
@@ -768,7 +767,7 @@
     <definedName name="ABRIL">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
     <definedName name="abs">#REF!</definedName>
     <definedName name="Acc">#REF!</definedName>
-    <definedName name="Access_Attribute">[2]Selections!$H$2:$H$4</definedName>
+    <definedName name="Access_Attribute">[1]Selections!$H$2:$H$4</definedName>
     <definedName name="Access_Button" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
     <definedName name="Access_Button1" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
     <definedName name="Access_Button2" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
@@ -785,7 +784,7 @@
     <definedName name="AIAOYE">InpMove7</definedName>
     <definedName name="AK">#REF!</definedName>
     <definedName name="ALE">#REF!</definedName>
-    <definedName name="Alert_Behaviour">[2]Selections!$G$2:$G$7</definedName>
+    <definedName name="Alert_Behaviour">[1]Selections!$G$2:$G$7</definedName>
     <definedName name="ALG_24">#REF!</definedName>
     <definedName name="ALG_24_low">#REF!</definedName>
     <definedName name="ALG_24_Std">#REF!</definedName>
@@ -825,7 +824,7 @@
     <definedName name="APR_Program_Pen">#REF!</definedName>
     <definedName name="apr_retail">#REF!</definedName>
     <definedName name="april">#REF!</definedName>
-    <definedName name="Area">[3]Selections!$I$1:$I$2</definedName>
+    <definedName name="Area">[2]Selections!$I$1:$I$2</definedName>
     <definedName name="AREA_COVER">#REF!</definedName>
     <definedName name="Arial">#REF!</definedName>
     <definedName name="as">#REF!</definedName>
@@ -839,7 +838,7 @@
     <definedName name="ATTACH4">#REF!</definedName>
     <definedName name="Attachment">#REF!</definedName>
     <definedName name="Attachment_4_all">#REF!</definedName>
-    <definedName name="Audience">[3]Selections!$C$1:$C$7</definedName>
+    <definedName name="Audience">[2]Selections!$C$1:$C$7</definedName>
     <definedName name="august">#REF!</definedName>
     <definedName name="B">#REF!</definedName>
     <definedName name="B\">#REF!</definedName>
@@ -891,7 +890,7 @@
     <definedName name="CHARTCURRENY">#REF!</definedName>
     <definedName name="check">#REF!</definedName>
     <definedName name="CHECK_1">"チェック 65"</definedName>
-    <definedName name="Check_Per_Cycle">[2]Selections!$J$2:$J$4</definedName>
+    <definedName name="Check_Per_Cycle">[1]Selections!$J$2:$J$4</definedName>
     <definedName name="Chicago">#REF!</definedName>
     <definedName name="cmprtl_dir">#REF!</definedName>
     <definedName name="Ｃｏ">#REF!</definedName>
@@ -976,7 +975,7 @@
     <definedName name="Dealer_Gross_Lease">#REF!</definedName>
     <definedName name="Dealer_Gross_Retail">#REF!</definedName>
     <definedName name="december">#REF!</definedName>
-    <definedName name="Decode_Type">[3]Selections!$F$1:$F$9</definedName>
+    <definedName name="Decode_Type">[2]Selections!$F$1:$F$9</definedName>
     <definedName name="Desc">#REF!</definedName>
     <definedName name="DEST">#REF!</definedName>
     <definedName name="ｄｆｄ">InpMove1</definedName>
@@ -988,7 +987,7 @@
     <definedName name="ＤＨ">#REF!</definedName>
     <definedName name="Di">#REF!</definedName>
     <definedName name="DIC">#REF!</definedName>
-    <definedName name="DID_Group">[3]Selections!$E$1:$E$6</definedName>
+    <definedName name="DID_Group">[2]Selections!$E$1:$E$6</definedName>
     <definedName name="digit_18">"テキスト 21"</definedName>
     <definedName name="Dimax">#REF!</definedName>
     <definedName name="Dimin">#REF!</definedName>
@@ -1013,7 +1012,7 @@
     <definedName name="ｄｓｄｓ">InpMove10</definedName>
     <definedName name="DSFGSDFG">#REF!</definedName>
     <definedName name="dsfsf" hidden="1">{"SUM GER",#N/A,FALSE,"SUM GER";"SUM FRA",#N/A,FALSE,"SUM FRA";"SUM ITA",#N/A,FALSE,"SUM ITA";"SUM SPA",#N/A,FALSE,"SUM SPA";"SUM EGB",#N/A,FALSE,"SUM EGB";"SUM IND",#N/A,FALSE,"SUM IND"}</definedName>
-    <definedName name="DTC_Class">[2]Selections!$F$2:$F$7</definedName>
+    <definedName name="DTC_Class">[1]Selections!$F$2:$F$7</definedName>
     <definedName name="DTEXT">#REF!</definedName>
     <definedName name="DUMMY">#REF!</definedName>
     <definedName name="ｄふぇｄふぇ">InpMove3</definedName>
@@ -1029,7 +1028,7 @@
     <definedName name="E50ﾄﾞﾗﾍﾙ西端" hidden="1">1</definedName>
     <definedName name="Eb">#REF!</definedName>
     <definedName name="EcartFranchise">#REF!</definedName>
-    <definedName name="ECUDID1">[4]Selections!$I$1:$I$2</definedName>
+    <definedName name="ECUDID1">[3]Selections!$I$1:$I$2</definedName>
     <definedName name="EE">#REF!</definedName>
     <definedName name="EE\">#REF!</definedName>
     <definedName name="EE\\">#REF!</definedName>
@@ -1107,7 +1106,7 @@
     <definedName name="Ｆａ">#REF!</definedName>
     <definedName name="FactoryResultUpdate">#REF!</definedName>
     <definedName name="fasdf" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
-    <definedName name="FaultList1">[5]Selections!$H$2:$H$4</definedName>
+    <definedName name="FaultList1">[4]Selections!$H$2:$H$4</definedName>
     <definedName name="ｆｃ">#REF!</definedName>
     <definedName name="FC_MES_MIX_CON_PROD_PARA_VANESSA">#REF!</definedName>
     <definedName name="fca">#REF!</definedName>
@@ -1237,7 +1236,7 @@
     <definedName name="hdfgh" hidden="1">{"SUM GER",#N/A,FALSE,"SUM GER";"SUM FRA",#N/A,FALSE,"SUM FRA";"SUM ITA",#N/A,FALSE,"SUM ITA";"SUM SPA",#N/A,FALSE,"SUM SPA";"SUM EGB",#N/A,FALSE,"SUM EGB";"SUM IND",#N/A,FALSE,"SUM IND"}</definedName>
     <definedName name="hdfghfg" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="HEV">#REF!</definedName>
-    <definedName name="Hex_LB">[6]Selections!$A$2:$A$103</definedName>
+    <definedName name="Hex_LB">[5]Selections!$A$2:$A$103</definedName>
     <definedName name="HF1_HARN">#N/A</definedName>
     <definedName name="ｈｇｈｆｇ">InpMove5</definedName>
     <definedName name="HH" hidden="1">#REF!</definedName>
@@ -1259,7 +1258,7 @@
     <definedName name="I\\\\\\">#REF!</definedName>
     <definedName name="IF">#REF!</definedName>
     <definedName name="II" hidden="1">#REF!</definedName>
-    <definedName name="Implementation">[3]Selections!$I$1:$I$2</definedName>
+    <definedName name="Implementation">[2]Selections!$I$1:$I$2</definedName>
     <definedName name="INC">#REF!</definedName>
     <definedName name="INDENT">#N/A</definedName>
     <definedName name="InterProductManage">#REF!</definedName>
@@ -1429,7 +1428,7 @@
     <definedName name="MCXvar">#REF!</definedName>
     <definedName name="MDL">#REF!</definedName>
     <definedName name="MDLYR">#REF!</definedName>
-    <definedName name="Memory">[3]Selections!$G$1:$G$4</definedName>
+    <definedName name="Memory">[2]Selections!$G$1:$G$4</definedName>
     <definedName name="Memphis_a">#REF!</definedName>
     <definedName name="MENU">#REF!</definedName>
     <definedName name="MENU1">#REF!</definedName>
@@ -1466,8 +1465,8 @@
     <definedName name="month3_direct">#REF!</definedName>
     <definedName name="month3_lease">#REF!</definedName>
     <definedName name="MOTO">#REF!</definedName>
-    <definedName name="MSB_LSB">[3]Selections!$B$1:$B$3</definedName>
-    <definedName name="MSB_LSB_List">[7]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB">[2]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB_List">[6]Selections!$B$1:$B$3</definedName>
     <definedName name="MSRP">#REF!</definedName>
     <definedName name="MSRP95">#REF!</definedName>
     <definedName name="MSRP96">#REF!</definedName>
@@ -1516,7 +1515,7 @@
     <definedName name="NNN">#REF!</definedName>
     <definedName name="no" localSheetId="0">#REF!</definedName>
     <definedName name="no">#REF!</definedName>
-    <definedName name="No_Yes">[3]Selections!$A$1:$A$3</definedName>
+    <definedName name="No_Yes">[2]Selections!$A$1:$A$3</definedName>
     <definedName name="Noff">#REF!</definedName>
     <definedName name="Ｎｏｓ">#REF!</definedName>
     <definedName name="Ｎｏｕｔ">#REF!</definedName>
@@ -1561,13 +1560,13 @@
     <definedName name="P_2">#REF!</definedName>
     <definedName name="P_3">#REF!</definedName>
     <definedName name="P_IMｸﾞﾗﾌ">#REF!</definedName>
-    <definedName name="P2_DIDs">[8]Ref_Ranges!$AI$2:$AI$3</definedName>
-    <definedName name="P2_ECUPins">OFFSET([9]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[9]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[9]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
-    <definedName name="P2_ECUType">[8]Header!$D$139:$D$150</definedName>
-    <definedName name="P2_ExtDataList">[8]Ref_Ranges!$AE$2:$AE$4</definedName>
-    <definedName name="P2_LSDIDList">[8]Ref_Ranges!$X$2:$X$4</definedName>
-    <definedName name="P2_SSD3SymtomValidator">[8]Ref_Ranges!$AK$2:$AK$3</definedName>
-    <definedName name="P2_Symptom_Validator">OFFSET([8]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[8]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[8]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
+    <definedName name="P2_DIDs">[7]Ref_Ranges!$AI$2:$AI$3</definedName>
+    <definedName name="P2_ECUPins">OFFSET([8]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[8]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[8]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
+    <definedName name="P2_ECUType">[7]Header!$D$139:$D$150</definedName>
+    <definedName name="P2_ExtDataList">[7]Ref_Ranges!$AE$2:$AE$4</definedName>
+    <definedName name="P2_LSDIDList">[7]Ref_Ranges!$X$2:$X$4</definedName>
+    <definedName name="P2_SSD3SymtomValidator">[7]Ref_Ranges!$AK$2:$AK$3</definedName>
+    <definedName name="P2_Symptom_Validator">OFFSET([7]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[7]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[7]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
     <definedName name="P6改" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="PACOST">#REF!</definedName>
     <definedName name="PAGE_4">#REF!</definedName>
@@ -1587,7 +1586,7 @@
     <definedName name="PATEXT">#REF!</definedName>
     <definedName name="Payment_24">#REF!</definedName>
     <definedName name="Payment_36">#REF!</definedName>
-    <definedName name="PBCU_Codes">[2]Selections!$D$2:$D$5</definedName>
+    <definedName name="PBCU_Codes">[1]Selections!$D$2:$D$5</definedName>
     <definedName name="PCAT">#REF!</definedName>
     <definedName name="PDSPEC">#REF!</definedName>
     <definedName name="PenRate">#REF!</definedName>
@@ -1648,7 +1647,7 @@
     <definedName name="PRINTSCOST">#REF!</definedName>
     <definedName name="PRINTVA">#REF!</definedName>
     <definedName name="PRINTW">#REF!</definedName>
-    <definedName name="Priority">[2]Selections!$I$2:$I$6</definedName>
+    <definedName name="Priority">[1]Selections!$I$2:$I$6</definedName>
     <definedName name="Prix">#REF!</definedName>
     <definedName name="PRT">#REF!</definedName>
     <definedName name="PSCOST">#REF!</definedName>
@@ -1680,7 +1679,7 @@
     <definedName name="QX4PR">#REF!</definedName>
     <definedName name="Q従業員名簿ｴｸｽﾎﾟｰﾄ用">#REF!</definedName>
     <definedName name="R_FLUSH_B1..M10">#REF!</definedName>
-    <definedName name="R_IO_W">[3]Selections!$D$1:$D$9</definedName>
+    <definedName name="R_IO_W">[2]Selections!$D$1:$D$9</definedName>
     <definedName name="RANGE">#REF!</definedName>
     <definedName name="RANGE1">#REF!</definedName>
     <definedName name="rango">#REF!</definedName>
@@ -1696,8 +1695,8 @@
     <definedName name="repurch_alamo">#REF!</definedName>
     <definedName name="repurch_base">#REF!</definedName>
     <definedName name="repurch_enter">#REF!</definedName>
-    <definedName name="Req_5" localSheetId="0">'[10]1.General'!#REF!</definedName>
-    <definedName name="Req_5">'[11]1.General'!#REF!</definedName>
+    <definedName name="Req_5" localSheetId="0">'[9]1.General'!#REF!</definedName>
+    <definedName name="Req_5">'[10]1.General'!#REF!</definedName>
     <definedName name="RES__24">#REF!</definedName>
     <definedName name="RES__36">#REF!</definedName>
     <definedName name="residual_support">#REF!</definedName>
@@ -1743,7 +1742,7 @@
     <definedName name="RYO">#REF!</definedName>
     <definedName name="ｒてれ">ｇｇｇｒ</definedName>
     <definedName name="ｒふぇえ">InpMove6</definedName>
-    <definedName name="s">[12]Selections!$I$2:$I$6</definedName>
+    <definedName name="s">[11]Selections!$I$2:$I$6</definedName>
     <definedName name="S\">#REF!</definedName>
     <definedName name="S\\">#REF!</definedName>
     <definedName name="S\\\">#REF!</definedName>
@@ -1767,7 +1766,7 @@
     <definedName name="ｓｄｓｗｗ">InpMove12</definedName>
     <definedName name="ｓｄふぁｓｆだｓｄふぁｓｆあせｆあｓｆだｓ">#REF!</definedName>
     <definedName name="se">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
-    <definedName name="Security_Required">[3]Selections!$H$1:$H$3</definedName>
+    <definedName name="Security_Required">[2]Selections!$H$1:$H$3</definedName>
     <definedName name="Segment_Sales">#REF!</definedName>
     <definedName name="segment_share">#REF!</definedName>
     <definedName name="SEINO">#REF!</definedName>
@@ -1828,7 +1827,7 @@
     <definedName name="temp">#REF!</definedName>
     <definedName name="TEST">#REF!</definedName>
     <definedName name="text">#REF!</definedName>
-    <definedName name="Text_LB">[2]Selections!$B$2:$B$103</definedName>
+    <definedName name="Text_LB">[1]Selections!$B$2:$B$103</definedName>
     <definedName name="texy">#REF!</definedName>
     <definedName name="ｔｇで">TMdatadisp1</definedName>
     <definedName name="TipoCambio">#REF!</definedName>
@@ -2010,8 +2009,8 @@
     <definedName name="Ｘ81Ｂ">#N/A</definedName>
     <definedName name="ｘ81ｂ01">#N/A</definedName>
     <definedName name="XX">#N/A</definedName>
-    <definedName name="xxa1">[13]DataBlock!#REF!</definedName>
-    <definedName name="xxx1">[13]DataBlock!#REF!</definedName>
+    <definedName name="xxa1">[12]DataBlock!#REF!</definedName>
+    <definedName name="xxx1">[12]DataBlock!#REF!</definedName>
     <definedName name="Y">#N/A</definedName>
     <definedName name="Y\">#REF!</definedName>
     <definedName name="Y\\">#REF!</definedName>
@@ -2019,12 +2018,12 @@
     <definedName name="Y\\\\">#REF!</definedName>
     <definedName name="Y\\\\\">#REF!</definedName>
     <definedName name="Y\\\\\\">#REF!</definedName>
-    <definedName name="yaa1">[13]DataBlock!#REF!</definedName>
+    <definedName name="yaa1">[12]DataBlock!#REF!</definedName>
     <definedName name="yes" localSheetId="0">#REF!</definedName>
     <definedName name="yes">#REF!</definedName>
-    <definedName name="yes_no">[2]Selections!$E$2:$E$3</definedName>
+    <definedName name="yes_no">[1]Selections!$E$2:$E$3</definedName>
     <definedName name="ｙｙｒｔ">#N/A</definedName>
-    <definedName name="yyy1">[13]DataBlock!#REF!</definedName>
+    <definedName name="yyy1">[12]DataBlock!#REF!</definedName>
     <definedName name="z" hidden="1">{"RESUMEN",#N/A,FALSE,"BASE ANEXOS";"ANEXO 1",#N/A,FALSE,"BASE ANEXOS";"ANEXO 2",#N/A,FALSE,"BASE ANEXOS"}</definedName>
     <definedName name="Z\">#REF!</definedName>
     <definedName name="Z\\">#REF!</definedName>
@@ -2048,7 +2047,7 @@
     <definedName name="Ｚｐｓ">#REF!</definedName>
     <definedName name="Ｚｓ">#REF!</definedName>
     <definedName name="ZZ" hidden="1">#REF!</definedName>
-    <definedName name="zzz1">[13]DataBlock!#REF!</definedName>
+    <definedName name="zzz1">[12]DataBlock!#REF!</definedName>
     <definedName name="α">#REF!</definedName>
     <definedName name="αf">#REF!</definedName>
     <definedName name="αm">#REF!</definedName>
@@ -2467,15 +2466,6 @@
   </si>
   <si>
     <t xml:space="preserve">
-0x0=Unsupported
-0x10 - 0x1F = STANDARD
-0x20 - 0x5F = Full Options
-0x60 - 0x8F = TECH
-0x90 - 0xFE = Reserved
-0xFF=Invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
 0x0= NA
 0x1= Vietnam
 0x2= ASEAN
@@ -2621,6 +2611,249 @@
 0x1=Without ORVM: heated
 0x2=With ORVM: heated
 0xF=Invalid</t>
+  </si>
+  <si>
+    <t>0x00 = Unsupported
+0x10 = STANDARD
+0x11 = STANDARD
+0x12 = STANDARD
+0x13 = STANDARD
+0x14 = STANDARD
+0x15 = STANDARD
+0x16 = STANDARD
+0x17 = STANDARD
+0x18 = STANDARD
+0x19 = STANDARD
+0x1A = STANDARD
+0x1B = STANDARD
+0x1C = STANDARD
+0x1D = STANDARD
+0x1E = STANDARD
+0x1F = STANDARD
+0x20 = Full Options
+0x21 = Full Options
+0x22 = Full Options
+0x23 = Full Options
+0x24 = Full Options
+0x25 = Full Options
+0x26 = Full Options
+0x27 = Full Options
+0x28 = Full Options
+0x29 = Full Options
+0x2A = Full Options
+0x2B = Full Options
+0x2C = Full Options
+0x2D = Full Options
+0x2E = Full Options
+0x2F = Full Options
+0x30 = Full Options
+0x31 = Full Options
+0x32 = Full Options
+0x33 = Full Options
+0x34 = Full Options
+0x35 = Full Options
+0x36 = Full Options
+0x37 = Full Options
+0x38 = Full Options
+0x39 = Full Options
+0x3A = Full Options
+0x3B = Full Options
+0x3C = Full Options
+0x3D = Full Options
+0x3E = Full Options
+0x3F = Full Options
+0x40 = Full Options
+0x41 = Full Options
+0x42 = Full Options
+0x43 = Full Options
+0x44 = Full Options
+0x45 = Full Options
+0x46 = Full Options
+0x47 = Full Options
+0x48 = Full Options
+0x49 = Full Options
+0x4A = Full Options
+0x4B = Full Options
+0x4C = Full Options
+0x4D = Full Options
+0x4E = Full Options
+0x4F = Full Options
+0x50 = Full Options
+0x51 = Full Options
+0x52 = Full Options
+0x53 = Full Options
+0x54 = Full Options
+0x55 = Full Options
+0x56 = Full Options
+0x57 = Full Options
+0x58 = Full Options
+0x59 = Full Options
+0x5A = Full Options
+0x5B = Full Options
+0x5C = Full Options
+0x5D = Full Options
+0x5E = Full Options
+0x5F = Full Options
+0x60 = TECH
+0x61 = TECH
+0x62 = TECH
+0x63 = TECH
+0x64 = TECH
+0x65 = TECH
+0x66 = TECH
+0x67 = TECH
+0x68 = TECH
+0x69 = TECH
+0x6A = TECH
+0x6B = TECH
+0x6C = TECH
+0x6D = TECH
+0x6E = TECH
+0x6F = TECH
+0x70 = TECH
+0x71 = TECH
+0x72 = TECH
+0x73 = TECH
+0x74 = TECH
+0x75 = TECH
+0x76 = TECH
+0x77 = TECH
+0x78 = TECH
+0x79 = TECH
+0x7A = TECH
+0x7B = TECH
+0x7C = TECH
+0x7D = TECH
+0x7E = TECH
+0x7F = TECH
+0x80 = TECH
+0x81 = TECH
+0x82 = TECH
+0x83 = TECH
+0x84 = TECH
+0x85 = TECH
+0x86 = TECH
+0x87 = TECH
+0x88 = TECH
+0x89 = TECH
+0x8A = TECH
+0x8B = TECH
+0x8C = TECH
+0x8D = TECH
+0x8E = TECH
+0x8F = TECH
+0x90 = Reserved
+0x91 = Reserved
+0x92 = Reserved
+0x93 = Reserved
+0x94 = Reserved
+0x95 = Reserved
+0x96 = Reserved
+0x97 = Reserved
+0x98 = Reserved
+0x99 = Reserved
+0x9A = Reserved
+0x9B = Reserved
+0x9C = Reserved
+0x9D = Reserved
+0x9E = Reserved
+0x9F = Reserved
+0xA0 = Reserved
+0xA1 = Reserved
+0xA2 = Reserved
+0xA3 = Reserved
+0xA4 = Reserved
+0xA5 = Reserved
+0xA6 = Reserved
+0xA7 = Reserved
+0xA8 = Reserved
+0xA9 = Reserved
+0xAA = Reserved
+0xAB = Reserved
+0xAC = Reserved
+0xAD = Reserved
+0xAE = Reserved
+0xAF = Reserved
+0xB0 = Reserved
+0xB1 = Reserved
+0xB2 = Reserved
+0xB3 = Reserved
+0xB4 = Reserved
+0xB5 = Reserved
+0xB6 = Reserved
+0xB7 = Reserved
+0xB8 = Reserved
+0xB9 = Reserved
+0xBA = Reserved
+0xBB = Reserved
+0xBC = Reserved
+0xBD = Reserved
+0xBE = Reserved
+0xBF = Reserved
+0xC0 = Reserved
+0xC1 = Reserved
+0xC2 = Reserved
+0xC3 = Reserved
+0xC4 = Reserved
+0xC5 = Reserved
+0xC6 = Reserved
+0xC7 = Reserved
+0xC8 = Reserved
+0xC9 = Reserved
+0xCA = Reserved
+0xCB = Reserved
+0xCC = Reserved
+0xCD = Reserved
+0xCE = Reserved
+0xCF = Reserved
+0xD0 = Reserved
+0xD1 = Reserved
+0xD2 = Reserved
+0xD3 = Reserved
+0xD4 = Reserved
+0xD5 = Reserved
+0xD6 = Reserved
+0xD7 = Reserved
+0xD8 = Reserved
+0xD9 = Reserved
+0xDA = Reserved
+0xDB = Reserved
+0xDC = Reserved
+0xDD = Reserved
+0xDE = Reserved
+0xDF = Reserved
+0xE0 = Reserved
+0xE1 = Reserved
+0xE2 = Reserved
+0xE3 = Reserved
+0xE4 = Reserved
+0xE5 = Reserved
+0xE6 = Reserved
+0xE7 = Reserved
+0xE8 = Reserved
+0xE9 = Reserved
+0xEA = Reserved
+0xEB = Reserved
+0xEC = Reserved
+0xED = Reserved
+0xEE = Reserved
+0xEF = Reserved
+0xF0 = Reserved
+0xF1 = Reserved
+0xF2 = Reserved
+0xF3 = Reserved
+0xF4 = Reserved
+0xF5 = Reserved
+0xF6 = Reserved
+0xF7 = Reserved
+0xF8 = Reserved
+0xF9 = Reserved
+0xFA = Reserved
+0xFB = Reserved
+0xFC = Reserved
+0xFD = Reserved
+0xFE = Reserved
+0xFF = Invalid</t>
   </si>
 </sst>
 </file>
@@ -2884,32 +3117,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3051,6 +3272,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3698,111 +3931,940 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Document Regulation"/>
-      <sheetName val="Change Log &amp; General Info"/>
-      <sheetName val="Diagnostics Services"/>
-      <sheetName val="System DID"/>
-      <sheetName val="ECU DID"/>
-      <sheetName val="DTC-List"/>
-      <sheetName val="FTB_RepairAction Refer"/>
-      <sheetName val="ECU Component data sheet"/>
-      <sheetName val="Snapshot DIDs"/>
-      <sheetName val="Extended Data"/>
-      <sheetName val="Routines Data (0x31)"/>
-      <sheetName val="Basic DIDs Check"/>
-      <sheetName val="Write VIN"/>
-      <sheetName val="ECU Exchange"/>
-      <sheetName val="Flashing Sequence"/>
-      <sheetName val="VOD Coding"/>
-      <sheetName val="CDS Coding"/>
-      <sheetName val="IO Control (2F)"/>
-      <sheetName val="Calibration Sequence"/>
-      <sheetName val="Key Fob Learn"/>
-      <sheetName val="IMMO Key Writing"/>
-      <sheetName val="Write TPMS ID"/>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Fault List"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fauth_List_Future"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Notes"/>
+      <sheetName val="SelfTestDTC"/>
+      <sheetName val="DTC Guidelines"/>
+      <sheetName val="PDU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>no sub type information</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>Body</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>No</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>A1</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>MO</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>Gen</v>
+          </cell>
+          <cell r="I2">
+            <v>1</v>
+          </cell>
+          <cell r="J2" t="str">
+            <v>OPC</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>01</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>General Electrical Failure</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Chassis</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Yes</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>A2</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>WLO</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>Dev</v>
+          </cell>
+          <cell r="I3">
+            <v>2</v>
+          </cell>
+          <cell r="J3" t="str">
+            <v>MPC</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>02</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>General signal failure</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>Network</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>B</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>WLB</v>
+          </cell>
+          <cell r="I4">
+            <v>3</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>See FDC Strategy Columns</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>03</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>FM (Frequency Modulated) / PWM (Pulse Width Modulated) Failure</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Powertrain</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>C</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Generic Warning Text</v>
+          </cell>
+          <cell r="I5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>04</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>System Internal Failures</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>D</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>Specific Warning Text</v>
+          </cell>
+          <cell r="I6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>05</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>System Programming Failures</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>E</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>None</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>06</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Algorithm Based Failures</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>07</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Mechanical Failures</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>08</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Bus Signal / Message Failures</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>09</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Component Failures</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>circuit short to ground</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>circuit short to battery</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>circuit open</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>circuit short to ground or open</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>circuit short to battery or open</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>circuit voltage below threshold</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>circuit voltage above threshold</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>circuit current below threshold</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>circuit current above threshold</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>1A</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>circuit resistance below threshold</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>1B</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>circuit resistance above threshold</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>1C</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>circuit voltage out of range</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>1D</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>circuit current out of range</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>1E</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>circuit resistance out of range</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>1F</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>circuit intermittent</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>21</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>signal amplitude &lt; minimum</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>22</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>signal amplitude &gt; maximum</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>23</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>signal stuck low</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>24</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>signal stuck high</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>25</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>signal shape / waveform failure</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>26</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>signal rate of change below threshold</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>27</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>signal rate of change above threshold</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>28</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>signal bias level out of range / zero adjustment failure</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>29</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>signal invalid</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>2A</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>signal stuck in range</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>2B</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>signal cross coupled</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>2F</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>signal erratic</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>31</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>No Signal</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>32</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Signal Low Time &lt; Minimum</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>33</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Signal Low Time &gt; Maximum</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>34</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Signal High Time &lt; Minimum</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>35</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Signal High Time &gt; Maximum</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>36</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Signal Frequency Too Low</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>37</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>Signal Frequency Too High</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>38</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>Signal Frequency Incorrect</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>39</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>Signal Has Too Few Pulses</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>3A</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>Signal Has Too Many Pulses</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>41</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>general checksum failure</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>42</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>general memory failure</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>43</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>special memory failure</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>44</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>data memory failure</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>45</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>program memory failure</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>46</v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>calibration / parameter memory failure</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>47</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>watchdog / safety MicroController failure</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>48</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>supervision software failure</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>49</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>internal electronic failure</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>4A</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>Incorrect Component Installed</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>4B</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>over temperature</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>51</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>not programmed</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>52</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>not activated</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>53</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>deactivated</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>54</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>missing calibration</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>55</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>not configured</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>56</v>
+          </cell>
+          <cell r="B65" t="str">
+            <v>Invalid / incomplete configuration</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>57</v>
+          </cell>
+          <cell r="B66" t="str">
+            <v>invalid / incomplete software component</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>61</v>
+          </cell>
+          <cell r="B67" t="str">
+            <v>signal calculation failure</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>62</v>
+          </cell>
+          <cell r="B68" t="str">
+            <v>signal compare failure</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>63</v>
+          </cell>
+          <cell r="B69" t="str">
+            <v>circuit / component protection time-out</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>64</v>
+          </cell>
+          <cell r="B70" t="str">
+            <v>signal plausibility failure</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>65</v>
+          </cell>
+          <cell r="B71" t="str">
+            <v>signal has too few transitions / events</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>66</v>
+          </cell>
+          <cell r="B72" t="str">
+            <v>signal has too many transitions / events</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>67</v>
+          </cell>
+          <cell r="B73" t="str">
+            <v>supervision software failure</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>68</v>
+          </cell>
+          <cell r="B74" t="str">
+            <v>event information</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>71</v>
+          </cell>
+          <cell r="B75" t="str">
+            <v>actuator stuck</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>72</v>
+          </cell>
+          <cell r="B76" t="str">
+            <v>actuator stuck open</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>73</v>
+          </cell>
+          <cell r="B77" t="str">
+            <v>actuator stuck closed</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>74</v>
+          </cell>
+          <cell r="B78" t="str">
+            <v>actuator slipping</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>75</v>
+          </cell>
+          <cell r="B79" t="str">
+            <v>emergency position not reachable</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>76</v>
+          </cell>
+          <cell r="B80" t="str">
+            <v>wrong mounting position</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>77</v>
+          </cell>
+          <cell r="B81" t="str">
+            <v>commanded position not reachable</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>78</v>
+          </cell>
+          <cell r="B82" t="str">
+            <v>alignment or adjustment incorrect</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>79</v>
+          </cell>
+          <cell r="B83" t="str">
+            <v xml:space="preserve">mechanical linkage failure </v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>7A</v>
+          </cell>
+          <cell r="B84" t="str">
+            <v>fluid leak or seal failure</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>7B</v>
+          </cell>
+          <cell r="B85" t="str">
+            <v>low fluid level</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>81</v>
+          </cell>
+          <cell r="B86" t="str">
+            <v>invalid serial data received</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>82</v>
+          </cell>
+          <cell r="B87" t="str">
+            <v>alive / sequence counter incorrect / not updated</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>83</v>
+          </cell>
+          <cell r="B88" t="str">
+            <v>value of signal protection calculation incorrect</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>84</v>
+          </cell>
+          <cell r="B89" t="str">
+            <v>signal below allowable range</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>85</v>
+          </cell>
+          <cell r="B90" t="str">
+            <v>signal above allowable range</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>86</v>
+          </cell>
+          <cell r="B91" t="str">
+            <v>signal invalid</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>87</v>
+          </cell>
+          <cell r="B92" t="str">
+            <v>missing message</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>88</v>
+          </cell>
+          <cell r="B93" t="str">
+            <v>bus off</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>8F</v>
+          </cell>
+          <cell r="B94" t="str">
+            <v>erratic</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>91</v>
+          </cell>
+          <cell r="B95" t="str">
+            <v>parametric</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>92</v>
+          </cell>
+          <cell r="B96" t="str">
+            <v>performance or incorrect operation</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>93</v>
+          </cell>
+          <cell r="B97" t="str">
+            <v>no operation</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>94</v>
+          </cell>
+          <cell r="B98" t="str">
+            <v>unexpected operation</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>95</v>
+          </cell>
+          <cell r="B99" t="str">
+            <v>incorrect assembly</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>96</v>
+          </cell>
+          <cell r="B100" t="str">
+            <v>component internal failure</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>97</v>
+          </cell>
+          <cell r="B101" t="str">
+            <v>Component or system operation obstructed or blocked</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>98</v>
+          </cell>
+          <cell r="B102" t="str">
+            <v>component or system over temperature</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>9A</v>
+          </cell>
+          <cell r="B103" t="str">
+            <v>component or system operating conditions</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Macro1"/>
-      <sheetName val="封面"/>
-      <sheetName val="RevisionRecords"/>
-      <sheetName val="Content"/>
-      <sheetName val="1.General"/>
-      <sheetName val="2.DiagnosticServices"/>
-      <sheetName val="3.TimingParameters"/>
-      <sheetName val="snFyHQ"/>
-      <sheetName val="4.1 DIDList"/>
-      <sheetName val="4.2 IODIDList"/>
-      <sheetName val="4.3 RoutineDIDList"/>
-      <sheetName val="5.1 DTCs list"/>
-      <sheetName val="5.2 Status of DTC"/>
-      <sheetName val="5.3 DTCSnapshot&amp;Extended"/>
-      <sheetName val="6.Security Access"/>
-      <sheetName val="discuss list"/>
-      <sheetName val="Ref_Ranges"/>
-      <sheetName val="Header"/>
-      <sheetName val="Selections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3849,7 +4911,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3876,7 +4938,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3945,942 +5007,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Fault List"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fauth_List_Future"/>
-      <sheetName val="Selections"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Notes"/>
-      <sheetName val="SelfTestDTC"/>
-      <sheetName val="DTC Guidelines"/>
-      <sheetName val="PDU"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>no sub type information</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Body</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>No</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>A1</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>MO</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>Gen</v>
-          </cell>
-          <cell r="I2">
-            <v>1</v>
-          </cell>
-          <cell r="J2" t="str">
-            <v>OPC</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>01</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>General Electrical Failure</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>Chassis</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>Yes</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>A2</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>WLO</v>
-          </cell>
-          <cell r="H3" t="str">
-            <v>Dev</v>
-          </cell>
-          <cell r="I3">
-            <v>2</v>
-          </cell>
-          <cell r="J3" t="str">
-            <v>MPC</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>02</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>General signal failure</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>Network</v>
-          </cell>
-          <cell r="F4" t="str">
-            <v>B</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>WLB</v>
-          </cell>
-          <cell r="I4">
-            <v>3</v>
-          </cell>
-          <cell r="J4" t="str">
-            <v>See FDC Strategy Columns</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>03</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>FM (Frequency Modulated) / PWM (Pulse Width Modulated) Failure</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>Powertrain</v>
-          </cell>
-          <cell r="F5" t="str">
-            <v>C</v>
-          </cell>
-          <cell r="G5" t="str">
-            <v>Generic Warning Text</v>
-          </cell>
-          <cell r="I5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>04</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>System Internal Failures</v>
-          </cell>
-          <cell r="F6" t="str">
-            <v>D</v>
-          </cell>
-          <cell r="G6" t="str">
-            <v>Specific Warning Text</v>
-          </cell>
-          <cell r="I6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>05</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>System Programming Failures</v>
-          </cell>
-          <cell r="F7" t="str">
-            <v>E</v>
-          </cell>
-          <cell r="G7" t="str">
-            <v>None</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>06</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Algorithm Based Failures</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>07</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Mechanical Failures</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>08</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Bus Signal / Message Failures</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>09</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Component Failures</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>11</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>circuit short to ground</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>12</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>circuit short to battery</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>13</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>circuit open</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>14</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>circuit short to ground or open</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>15</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>circuit short to battery or open</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>16</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>circuit voltage below threshold</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>17</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>circuit voltage above threshold</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>18</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>circuit current below threshold</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>19</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>circuit current above threshold</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>1A</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>circuit resistance below threshold</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>1B</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>circuit resistance above threshold</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>1C</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v>circuit voltage out of range</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>1D</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>circuit current out of range</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>1E</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>circuit resistance out of range</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>1F</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>circuit intermittent</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>21</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>signal amplitude &lt; minimum</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>22</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>signal amplitude &gt; maximum</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>23</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>signal stuck low</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>24</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>signal stuck high</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>25</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>signal shape / waveform failure</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>26</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>signal rate of change below threshold</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>27</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>signal rate of change above threshold</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>28</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>signal bias level out of range / zero adjustment failure</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>29</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>signal invalid</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>2A</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>signal stuck in range</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>2B</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>signal cross coupled</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>2F</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>signal erratic</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>31</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>No Signal</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>32</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Signal Low Time &lt; Minimum</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>33</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Signal Low Time &gt; Maximum</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>34</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Signal High Time &lt; Minimum</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>35</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Signal High Time &gt; Maximum</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>36</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Signal Frequency Too Low</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>37</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>Signal Frequency Too High</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>38</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Signal Frequency Incorrect</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>39</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Signal Has Too Few Pulses</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>3A</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Signal Has Too Many Pulses</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>41</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>general checksum failure</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>42</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>general memory failure</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>43</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>special memory failure</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>44</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>data memory failure</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>45</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>program memory failure</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>46</v>
-          </cell>
-          <cell r="B54" t="str">
-            <v>calibration / parameter memory failure</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>47</v>
-          </cell>
-          <cell r="B55" t="str">
-            <v>watchdog / safety MicroController failure</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>48</v>
-          </cell>
-          <cell r="B56" t="str">
-            <v>supervision software failure</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>49</v>
-          </cell>
-          <cell r="B57" t="str">
-            <v>internal electronic failure</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>4A</v>
-          </cell>
-          <cell r="B58" t="str">
-            <v>Incorrect Component Installed</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>4B</v>
-          </cell>
-          <cell r="B59" t="str">
-            <v>over temperature</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>51</v>
-          </cell>
-          <cell r="B60" t="str">
-            <v>not programmed</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>52</v>
-          </cell>
-          <cell r="B61" t="str">
-            <v>not activated</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>53</v>
-          </cell>
-          <cell r="B62" t="str">
-            <v>deactivated</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>54</v>
-          </cell>
-          <cell r="B63" t="str">
-            <v>missing calibration</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>55</v>
-          </cell>
-          <cell r="B64" t="str">
-            <v>not configured</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>56</v>
-          </cell>
-          <cell r="B65" t="str">
-            <v>Invalid / incomplete configuration</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>57</v>
-          </cell>
-          <cell r="B66" t="str">
-            <v>invalid / incomplete software component</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>61</v>
-          </cell>
-          <cell r="B67" t="str">
-            <v>signal calculation failure</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>62</v>
-          </cell>
-          <cell r="B68" t="str">
-            <v>signal compare failure</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>63</v>
-          </cell>
-          <cell r="B69" t="str">
-            <v>circuit / component protection time-out</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>64</v>
-          </cell>
-          <cell r="B70" t="str">
-            <v>signal plausibility failure</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>65</v>
-          </cell>
-          <cell r="B71" t="str">
-            <v>signal has too few transitions / events</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>66</v>
-          </cell>
-          <cell r="B72" t="str">
-            <v>signal has too many transitions / events</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>67</v>
-          </cell>
-          <cell r="B73" t="str">
-            <v>supervision software failure</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>68</v>
-          </cell>
-          <cell r="B74" t="str">
-            <v>event information</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>71</v>
-          </cell>
-          <cell r="B75" t="str">
-            <v>actuator stuck</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>72</v>
-          </cell>
-          <cell r="B76" t="str">
-            <v>actuator stuck open</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>73</v>
-          </cell>
-          <cell r="B77" t="str">
-            <v>actuator stuck closed</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>74</v>
-          </cell>
-          <cell r="B78" t="str">
-            <v>actuator slipping</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>75</v>
-          </cell>
-          <cell r="B79" t="str">
-            <v>emergency position not reachable</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>76</v>
-          </cell>
-          <cell r="B80" t="str">
-            <v>wrong mounting position</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>77</v>
-          </cell>
-          <cell r="B81" t="str">
-            <v>commanded position not reachable</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>78</v>
-          </cell>
-          <cell r="B82" t="str">
-            <v>alignment or adjustment incorrect</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>79</v>
-          </cell>
-          <cell r="B83" t="str">
-            <v xml:space="preserve">mechanical linkage failure </v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>7A</v>
-          </cell>
-          <cell r="B84" t="str">
-            <v>fluid leak or seal failure</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>7B</v>
-          </cell>
-          <cell r="B85" t="str">
-            <v>low fluid level</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>81</v>
-          </cell>
-          <cell r="B86" t="str">
-            <v>invalid serial data received</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>82</v>
-          </cell>
-          <cell r="B87" t="str">
-            <v>alive / sequence counter incorrect / not updated</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>83</v>
-          </cell>
-          <cell r="B88" t="str">
-            <v>value of signal protection calculation incorrect</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>84</v>
-          </cell>
-          <cell r="B89" t="str">
-            <v>signal below allowable range</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>85</v>
-          </cell>
-          <cell r="B90" t="str">
-            <v>signal above allowable range</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>86</v>
-          </cell>
-          <cell r="B91" t="str">
-            <v>signal invalid</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>87</v>
-          </cell>
-          <cell r="B92" t="str">
-            <v>missing message</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>88</v>
-          </cell>
-          <cell r="B93" t="str">
-            <v>bus off</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>8F</v>
-          </cell>
-          <cell r="B94" t="str">
-            <v>erratic</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>91</v>
-          </cell>
-          <cell r="B95" t="str">
-            <v>parametric</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>92</v>
-          </cell>
-          <cell r="B96" t="str">
-            <v>performance or incorrect operation</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>93</v>
-          </cell>
-          <cell r="B97" t="str">
-            <v>no operation</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>94</v>
-          </cell>
-          <cell r="B98" t="str">
-            <v>unexpected operation</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>95</v>
-          </cell>
-          <cell r="B99" t="str">
-            <v>incorrect assembly</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>96</v>
-          </cell>
-          <cell r="B100" t="str">
-            <v>component internal failure</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>97</v>
-          </cell>
-          <cell r="B101" t="str">
-            <v>Component or system operation obstructed or blocked</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>98</v>
-          </cell>
-          <cell r="B102" t="str">
-            <v>component or system over temperature</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>9A</v>
-          </cell>
-          <cell r="B103" t="str">
-            <v>component or system operating conditions</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="VF31 REQ External Discussion"/>
       <sheetName val="VFe34_GauTui_Requirement_Discus"/>
       <sheetName val="Selections"/>
@@ -4898,7 +5024,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4915,7 +5041,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4944,7 +5070,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5494,7 +5620,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5535,7 +5661,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5770,7 +5896,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6004,6 +6130,55 @@
       <sheetData sheetId="111"/>
       <sheetData sheetId="112" refreshError="1"/>
       <sheetData sheetId="113" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Macro1"/>
+      <sheetName val="封面"/>
+      <sheetName val="RevisionRecords"/>
+      <sheetName val="Content"/>
+      <sheetName val="1.General"/>
+      <sheetName val="2.DiagnosticServices"/>
+      <sheetName val="3.TimingParameters"/>
+      <sheetName val="snFyHQ"/>
+      <sheetName val="4.1 DIDList"/>
+      <sheetName val="4.2 IODIDList"/>
+      <sheetName val="4.3 RoutineDIDList"/>
+      <sheetName val="5.1 DTCs list"/>
+      <sheetName val="5.2 Status of DTC"/>
+      <sheetName val="5.3 DTCSnapshot&amp;Extended"/>
+      <sheetName val="6.Security Access"/>
+      <sheetName val="discuss list"/>
+      <sheetName val="Ref_Ranges"/>
+      <sheetName val="Header"/>
+      <sheetName val="Selections"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6372,659 +6547,659 @@
     <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="5" customFormat="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
+    <row r="2" spans="1:6" s="4" customFormat="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" ht="15">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+    <row r="3" spans="1:6" s="4" customFormat="1" ht="15">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:6" s="5" customFormat="1" ht="15">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+    <row r="4" spans="1:6" s="4" customFormat="1" ht="15">
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:6" s="5" customFormat="1" ht="15">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+    <row r="5" spans="1:6" s="4" customFormat="1" ht="15">
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:6" s="5" customFormat="1" ht="15">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+    <row r="6" spans="1:6" s="4" customFormat="1" ht="15">
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:6" s="1" customFormat="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:6" s="1" customFormat="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="9"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:6" s="1" customFormat="1" ht="14.4" thickBot="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" ht="27.6">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" ht="27.6">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="1" customFormat="1" ht="27.6">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="1" customFormat="1" ht="27.6">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="30">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" s="21" customFormat="1" ht="15">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20"/>
+    <row r="18" spans="1:6" s="17" customFormat="1" ht="15">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:6" ht="27.6">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="20"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="24"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" s="30" customFormat="1">
-      <c r="A21" s="25" t="s">
+    <row r="21" spans="1:6" s="26" customFormat="1">
+      <c r="A21" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="29"/>
+      <c r="E21" s="25"/>
     </row>
     <row r="22" spans="1:6" ht="30">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="24" t="s">
         <v>35</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" ht="27.6">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" ht="27.6">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" ht="14.4" thickBot="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="31" t="s">
         <v>7</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6">
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" s="38" customFormat="1">
-      <c r="A29" s="36" t="s">
+    <row r="29" spans="1:6" s="34" customFormat="1">
+      <c r="A29" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="33" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="42" customFormat="1">
-      <c r="A30" s="39" t="s">
+    <row r="30" spans="1:6" s="38" customFormat="1">
+      <c r="A30" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="36">
         <v>3</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="36">
         <v>0</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="36">
         <v>16</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="37"/>
     </row>
-    <row r="31" spans="1:6" s="42" customFormat="1">
-      <c r="A31" s="39" t="s">
+    <row r="31" spans="1:6" s="38" customFormat="1">
+      <c r="A31" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="36">
         <f t="shared" ref="B31" si="0">B30+QUOTIENT((D30+C30),8)</f>
         <v>5</v>
       </c>
-      <c r="C31" s="40">
+      <c r="C31" s="36">
         <f t="shared" ref="C31" si="1">MOD(C30+D30,8)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="36">
         <v>56</v>
       </c>
-      <c r="E31" s="41"/>
+      <c r="E31" s="37"/>
     </row>
-    <row r="32" spans="1:6" s="42" customFormat="1" ht="17.7" customHeight="1">
-      <c r="A32" s="43" t="s">
+    <row r="32" spans="1:6" s="38" customFormat="1" ht="17.7" customHeight="1">
+      <c r="A32" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="40">
         <v>12</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="45"/>
+      <c r="E32" s="41"/>
     </row>
-    <row r="33" spans="1:5" s="46" customFormat="1" ht="79.2">
-      <c r="A33" s="43" t="s">
+    <row r="33" spans="1:5" s="42" customFormat="1" ht="79.2">
+      <c r="A33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="40">
         <v>13</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="C33" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="45" t="s">
+      <c r="E33" s="41" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="46" customFormat="1" ht="92.4">
-      <c r="A34" s="43" t="s">
+    <row r="34" spans="1:5" s="42" customFormat="1" ht="409.6">
+      <c r="A34" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="40">
         <v>14</v>
       </c>
-      <c r="C34" s="44" t="s">
+      <c r="C34" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="44" t="s">
+      <c r="D34" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="45" t="s">
+      <c r="E34" s="41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="42" customFormat="1" ht="330">
+      <c r="A35" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="40">
+        <v>15</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="40">
+        <v>8</v>
+      </c>
+      <c r="E35" s="41" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="46" customFormat="1" ht="330">
-      <c r="A35" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="44">
-        <v>15</v>
-      </c>
-      <c r="C35" s="44" t="s">
+    <row r="36" spans="1:5" s="42" customFormat="1" ht="409.6">
+      <c r="A36" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="40">
+        <v>16</v>
+      </c>
+      <c r="C36" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D36" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="42" customFormat="1">
+      <c r="A37" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="44">
+        <v>17</v>
+      </c>
+      <c r="C37" s="44">
+        <v>0</v>
+      </c>
+      <c r="D37" s="44">
         <v>8</v>
       </c>
-      <c r="E35" s="45" t="s">
-        <v>69</v>
-      </c>
+      <c r="E37" s="45"/>
     </row>
-    <row r="36" spans="1:5" s="46" customFormat="1" ht="409.6">
-      <c r="A36" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="44">
-        <v>16</v>
-      </c>
-      <c r="C36" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="45" t="s">
+    <row r="38" spans="1:5" s="42" customFormat="1">
+      <c r="A38" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="44">
+        <v>18</v>
+      </c>
+      <c r="C38" s="44">
+        <v>4</v>
+      </c>
+      <c r="D38" s="44">
+        <v>8</v>
+      </c>
+      <c r="E38" s="45"/>
+    </row>
+    <row r="39" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A39" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="46">
+        <v>19</v>
+      </c>
+      <c r="C39" s="46">
+        <v>0</v>
+      </c>
+      <c r="D39" s="46">
+        <v>4</v>
+      </c>
+      <c r="E39" s="47" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="46" customFormat="1">
-      <c r="A37" s="47" t="s">
+    <row r="40" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A40" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="48">
+        <v>19</v>
+      </c>
+      <c r="C40" s="48">
+        <v>4</v>
+      </c>
+      <c r="D40" s="48">
+        <v>4</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A41" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="46">
+        <v>20</v>
+      </c>
+      <c r="C41" s="46">
+        <v>0</v>
+      </c>
+      <c r="D41" s="46">
+        <v>4</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A42" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="46">
+        <v>20</v>
+      </c>
+      <c r="C42" s="46">
+        <v>4</v>
+      </c>
+      <c r="D42" s="46">
+        <v>4</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="42" customFormat="1">
+      <c r="A43" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="48">
-        <v>17</v>
-      </c>
-      <c r="C37" s="48">
+      <c r="B43" s="44">
+        <v>21</v>
+      </c>
+      <c r="C43" s="44">
         <v>0</v>
       </c>
-      <c r="D37" s="48">
+      <c r="D43" s="44">
         <v>8</v>
       </c>
-      <c r="E37" s="49"/>
+      <c r="E43" s="45"/>
     </row>
-    <row r="38" spans="1:5" s="46" customFormat="1">
-      <c r="A38" s="47" t="s">
+    <row r="44" spans="1:5" s="42" customFormat="1" ht="79.2">
+      <c r="A44" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="51">
+        <v>22</v>
+      </c>
+      <c r="C44" s="51">
+        <v>0</v>
+      </c>
+      <c r="D44" s="51">
+        <v>4</v>
+      </c>
+      <c r="E44" s="52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="42" customFormat="1">
+      <c r="A45" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="48">
-        <v>18</v>
-      </c>
-      <c r="C38" s="48">
+      <c r="B45" s="44">
+        <v>22</v>
+      </c>
+      <c r="C45" s="44">
         <v>4</v>
       </c>
-      <c r="D38" s="48">
+      <c r="D45" s="44">
+        <v>4</v>
+      </c>
+      <c r="E45" s="45"/>
+    </row>
+    <row r="46" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A46" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="51">
+        <v>23</v>
+      </c>
+      <c r="C46" s="51">
+        <v>0</v>
+      </c>
+      <c r="D46" s="51">
+        <v>4</v>
+      </c>
+      <c r="E46" s="52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A47" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="51">
+        <v>23</v>
+      </c>
+      <c r="C47" s="51">
+        <v>4</v>
+      </c>
+      <c r="D47" s="51">
+        <v>4</v>
+      </c>
+      <c r="E47" s="52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="42" customFormat="1" ht="79.2">
+      <c r="A48" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="51">
+        <v>24</v>
+      </c>
+      <c r="C48" s="51">
+        <v>0</v>
+      </c>
+      <c r="D48" s="51">
+        <v>4</v>
+      </c>
+      <c r="E48" s="52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="42" customFormat="1" ht="66">
+      <c r="A49" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="51">
+        <v>24</v>
+      </c>
+      <c r="C49" s="51">
+        <v>4</v>
+      </c>
+      <c r="D49" s="51">
+        <v>4</v>
+      </c>
+      <c r="E49" s="52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="42" customFormat="1">
+      <c r="A50" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="54">
+        <v>61</v>
+      </c>
+      <c r="C50" s="36">
+        <v>0</v>
+      </c>
+      <c r="D50" s="36">
         <v>8</v>
       </c>
-      <c r="E38" s="49"/>
-    </row>
-    <row r="39" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A39" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="50">
-        <v>19</v>
-      </c>
-      <c r="C39" s="50">
-        <v>0</v>
-      </c>
-      <c r="D39" s="50">
-        <v>4</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A40" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="52">
-        <v>19</v>
-      </c>
-      <c r="C40" s="52">
-        <v>4</v>
-      </c>
-      <c r="D40" s="52">
-        <v>4</v>
-      </c>
-      <c r="E40" s="53" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A41" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="50">
-        <v>20</v>
-      </c>
-      <c r="C41" s="50">
-        <v>0</v>
-      </c>
-      <c r="D41" s="50">
-        <v>4</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A42" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="50">
-        <v>20</v>
-      </c>
-      <c r="C42" s="50">
-        <v>4</v>
-      </c>
-      <c r="D42" s="50">
-        <v>4</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="46" customFormat="1">
-      <c r="A43" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="48">
-        <v>21</v>
-      </c>
-      <c r="C43" s="48">
-        <v>0</v>
-      </c>
-      <c r="D43" s="48">
-        <v>8</v>
-      </c>
-      <c r="E43" s="49"/>
-    </row>
-    <row r="44" spans="1:5" s="46" customFormat="1" ht="79.2">
-      <c r="A44" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" s="55">
-        <v>22</v>
-      </c>
-      <c r="C44" s="55">
-        <v>0</v>
-      </c>
-      <c r="D44" s="55">
-        <v>4</v>
-      </c>
-      <c r="E44" s="56" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="46" customFormat="1">
-      <c r="A45" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="48">
-        <v>22</v>
-      </c>
-      <c r="C45" s="48">
-        <v>4</v>
-      </c>
-      <c r="D45" s="48">
-        <v>4</v>
-      </c>
-      <c r="E45" s="49"/>
-    </row>
-    <row r="46" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A46" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="55">
-        <v>23</v>
-      </c>
-      <c r="C46" s="55">
-        <v>0</v>
-      </c>
-      <c r="D46" s="55">
-        <v>4</v>
-      </c>
-      <c r="E46" s="56" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A47" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="55">
-        <v>23</v>
-      </c>
-      <c r="C47" s="55">
-        <v>4</v>
-      </c>
-      <c r="D47" s="55">
-        <v>4</v>
-      </c>
-      <c r="E47" s="56" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="46" customFormat="1" ht="79.2">
-      <c r="A48" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="55">
-        <v>24</v>
-      </c>
-      <c r="C48" s="55">
-        <v>0</v>
-      </c>
-      <c r="D48" s="55">
-        <v>4</v>
-      </c>
-      <c r="E48" s="56" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="46" customFormat="1" ht="66">
-      <c r="A49" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" s="55">
-        <v>24</v>
-      </c>
-      <c r="C49" s="55">
-        <v>4</v>
-      </c>
-      <c r="D49" s="55">
-        <v>4</v>
-      </c>
-      <c r="E49" s="56" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="46" customFormat="1">
-      <c r="A50" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" s="58">
-        <v>61</v>
-      </c>
-      <c r="C50" s="40">
-        <v>0</v>
-      </c>
-      <c r="D50" s="40">
-        <v>8</v>
-      </c>
-      <c r="E50" s="39"/>
+      <c r="E50" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7044,13 +7219,13 @@
     <cfRule type="duplicateValues" dxfId="50" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="49" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="57"/>
     <cfRule type="duplicateValues" dxfId="45" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36 A32:A34">
     <cfRule type="duplicateValues" dxfId="42" priority="54"/>
@@ -7072,44 +7247,44 @@
     <cfRule type="duplicateValues" dxfId="30" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:A40">
-    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="43"/>
     <cfRule type="duplicateValues" dxfId="27" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="40"/>
     <cfRule type="duplicateValues" dxfId="24" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
-    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
     <cfRule type="duplicateValues" dxfId="20" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42">
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
     <cfRule type="duplicateValues" dxfId="16" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
     <cfRule type="duplicateValues" dxfId="14" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
     <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
     <cfRule type="duplicateValues" dxfId="2" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51111111111111096" footer="0.51111111111111096"/>
   <pageSetup paperSize="9" orientation="portrait"/>
